--- a/에너지경제학/자원에너지경제학 01분반_주_2026201648_출결학습현황_학습요소별보기_20261020_1438.xlsx
+++ b/에너지경제학/자원에너지경제학 01분반_주_2026201648_출결학습현황_학습요소별보기_20261020_1438.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30527"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sidus\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DESKTOP\Desktop\00_Teaching\에너지경제학\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{842BFE5C-B1E9-420E-99F6-FD1C606E4451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F5E8C98-D630-4845-AA8F-4279E864890D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,6 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Worksheet!$A$4:$E$4</definedName>
     <definedName name="_xlchart.v1.0" hidden="1">Worksheet!$C$5:$C$43</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Worksheet!$C$5:$C$43</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1006,8 +1005,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="6153150" y="2705100"/>
-              <a:ext cx="4572000" cy="2743200"/>
+              <a:off x="6384925" y="2628900"/>
+              <a:ext cx="4572000" cy="2654300"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1328,30 +1327,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:E44"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.28515625" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.26953125" customWidth="1"/>
+    <col min="4" max="4" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
     </row>
-    <row r="4" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="17" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -1368,7 +1367,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1376,7 +1375,7 @@
         <v>9</v>
       </c>
       <c r="C5">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
         <v>10</v>
@@ -1385,7 +1384,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>26</v>
       </c>
@@ -1402,7 +1401,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>18</v>
       </c>
@@ -1419,7 +1418,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>20</v>
       </c>
@@ -1436,7 +1435,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>1</v>
       </c>
@@ -1453,7 +1452,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>13</v>
       </c>
@@ -1470,7 +1469,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>38</v>
       </c>
@@ -1487,7 +1486,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1504,7 +1503,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>19</v>
       </c>
@@ -1521,7 +1520,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>34</v>
       </c>
@@ -1538,7 +1537,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>2</v>
       </c>
@@ -1555,7 +1554,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1572,7 +1571,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>31</v>
       </c>
@@ -1589,7 +1588,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>6</v>
       </c>
@@ -1606,7 +1605,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>37</v>
       </c>
@@ -1623,7 +1622,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>32</v>
       </c>
@@ -1640,7 +1639,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>16</v>
       </c>
@@ -1657,7 +1656,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>24</v>
       </c>
@@ -1674,7 +1673,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>23</v>
       </c>
@@ -1691,7 +1690,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>12</v>
       </c>
@@ -1708,7 +1707,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>33</v>
       </c>
@@ -1725,7 +1724,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>21</v>
       </c>
@@ -1742,7 +1741,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>30</v>
       </c>
@@ -1759,7 +1758,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>39</v>
       </c>
@@ -1776,7 +1775,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>25</v>
       </c>
@@ -1793,7 +1792,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>9</v>
       </c>
@@ -1810,7 +1809,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>4</v>
       </c>
@@ -1827,7 +1826,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>8</v>
       </c>
@@ -1844,7 +1843,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>40</v>
       </c>
@@ -1861,7 +1860,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>10</v>
       </c>
@@ -1878,7 +1877,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>28</v>
       </c>
@@ -1895,7 +1894,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
@@ -1912,7 +1911,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>17</v>
       </c>
@@ -1929,7 +1928,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>7</v>
       </c>
@@ -1946,7 +1945,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>29</v>
       </c>
@@ -1963,7 +1962,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>22</v>
       </c>
@@ -1980,7 +1979,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>27</v>
       </c>
@@ -1997,7 +1996,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>36</v>
       </c>
@@ -2014,7 +2013,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>5</v>
       </c>
@@ -2031,7 +2030,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>15</v>
       </c>

--- a/에너지경제학/자원에너지경제학 01분반_주_2026201648_출결학습현황_학습요소별보기_20261020_1438.xlsx
+++ b/에너지경제학/자원에너지경제학 01분반_주_2026201648_출결학습현황_학습요소별보기_20261020_1438.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DESKTOP\Desktop\00_Teaching\에너지경제학\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F5E8C98-D630-4845-AA8F-4279E864890D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D66838C-2905-4B26-9D6C-78FB80C10DF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,6 +18,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Worksheet!$A$4:$E$4</definedName>
     <definedName name="_xlchart.v1.0" hidden="1">Worksheet!$C$5:$C$43</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">Worksheet!$C$5:$C$43</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">Worksheet!$C$5:$C$43</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -315,6 +317,7 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
@@ -377,7 +380,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.0</cx:f>
+        <cx:f>_xlchart.v1.1</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -960,16 +963,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>561975</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>333375</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>257175</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
@@ -1005,7 +1008,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="6384925" y="2628900"/>
+              <a:off x="7527925" y="2832100"/>
               <a:ext cx="4572000" cy="2654300"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1326,7 +1329,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:E44"/>
+  <dimension ref="A2:G44"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
@@ -1336,21 +1339,21 @@
     <col min="5" max="5" width="10.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
     </row>
-    <row r="4" spans="1:5" ht="17" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:7" ht="17" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -1367,7 +1370,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1383,8 +1386,12 @@
       <c r="E5" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G5">
+        <f>AVERAGE(C5:C43)</f>
+        <v>54.692307692307693</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>26</v>
       </c>
@@ -1401,7 +1408,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>18</v>
       </c>
@@ -1418,7 +1425,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>20</v>
       </c>
@@ -1435,7 +1442,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>1</v>
       </c>
@@ -1452,7 +1459,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>13</v>
       </c>
@@ -1469,7 +1476,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>38</v>
       </c>
@@ -1486,7 +1493,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1503,7 +1510,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>19</v>
       </c>
@@ -1520,7 +1527,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>34</v>
       </c>
@@ -1537,7 +1544,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>2</v>
       </c>
@@ -1554,7 +1561,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>14</v>
       </c>
